--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121393568</v>
+        <v>121392173</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502665</v>
+        <v>502708</v>
       </c>
       <c r="R2" t="n">
-        <v>6980853</v>
+        <v>6980897</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392330</v>
+        <v>121392324</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502707</v>
+        <v>502722</v>
       </c>
       <c r="R3" t="n">
-        <v>6980894</v>
+        <v>6980906</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393565</v>
+        <v>121393568</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502666</v>
+        <v>502665</v>
       </c>
       <c r="R4" t="n">
-        <v>6980854</v>
+        <v>6980853</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121392997</v>
+        <v>121393565</v>
       </c>
       <c r="B5" t="n">
         <v>90697</v>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502612</v>
+        <v>502666</v>
       </c>
       <c r="R5" t="n">
-        <v>6980880</v>
+        <v>6980854</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392194</v>
+        <v>121393539</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502707</v>
+        <v>502656</v>
       </c>
       <c r="R6" t="n">
-        <v>6980905</v>
+        <v>6980868</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391948</v>
+        <v>121392330</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502812</v>
+        <v>502707</v>
       </c>
       <c r="R7" t="n">
-        <v>6980986</v>
+        <v>6980894</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392324</v>
+        <v>121391948</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502722</v>
+        <v>502812</v>
       </c>
       <c r="R9" t="n">
-        <v>6980906</v>
+        <v>6980986</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121393539</v>
+        <v>121392997</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502656</v>
+        <v>502612</v>
       </c>
       <c r="R10" t="n">
-        <v>6980868</v>
+        <v>6980880</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392173</v>
+        <v>121392194</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,34 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502708</v>
+        <v>502707</v>
       </c>
       <c r="R11" t="n">
-        <v>6980897</v>
+        <v>6980905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,6 +1780,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392173</v>
+        <v>121392997</v>
       </c>
       <c r="B2" t="n">
         <v>90697</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502708</v>
+        <v>502612</v>
       </c>
       <c r="R2" t="n">
-        <v>6980897</v>
+        <v>6980880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393568</v>
+        <v>121392173</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502665</v>
+        <v>502708</v>
       </c>
       <c r="R4" t="n">
-        <v>6980853</v>
+        <v>6980897</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393565</v>
+        <v>121393568</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502666</v>
+        <v>502665</v>
       </c>
       <c r="R5" t="n">
-        <v>6980854</v>
+        <v>6980853</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121393539</v>
+        <v>121392512</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502656</v>
+        <v>502643</v>
       </c>
       <c r="R6" t="n">
-        <v>6980868</v>
+        <v>6980884</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392330</v>
+        <v>121391948</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502707</v>
+        <v>502812</v>
       </c>
       <c r="R7" t="n">
-        <v>6980894</v>
+        <v>6980986</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121392512</v>
+        <v>121393565</v>
       </c>
       <c r="B8" t="n">
         <v>90697</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502643</v>
+        <v>502666</v>
       </c>
       <c r="R8" t="n">
-        <v>6980884</v>
+        <v>6980854</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121391948</v>
+        <v>121392194</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,37 +1475,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502812</v>
+        <v>502707</v>
       </c>
       <c r="R9" t="n">
-        <v>6980986</v>
+        <v>6980905</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392997</v>
+        <v>121393539</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1615,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502612</v>
+        <v>502656</v>
       </c>
       <c r="R10" t="n">
-        <v>6980880</v>
+        <v>6980868</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392194</v>
+        <v>121392330</v>
       </c>
       <c r="B11" t="n">
         <v>90983</v>
@@ -1717,9 +1721,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
@@ -1729,10 +1730,10 @@
         <v>502707</v>
       </c>
       <c r="R11" t="n">
-        <v>6980905</v>
+        <v>6980894</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1781,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392512</v>
+        <v>121391948</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502643</v>
+        <v>502812</v>
       </c>
       <c r="R6" t="n">
-        <v>6980884</v>
+        <v>6980986</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391948</v>
+        <v>121392512</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502812</v>
+        <v>502643</v>
       </c>
       <c r="R7" t="n">
-        <v>6980986</v>
+        <v>6980884</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392997</v>
+        <v>121392330</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502612</v>
+        <v>502707</v>
       </c>
       <c r="R2" t="n">
-        <v>6980880</v>
+        <v>6980894</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392324</v>
+        <v>121392173</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502722</v>
+        <v>502708</v>
       </c>
       <c r="R3" t="n">
-        <v>6980906</v>
+        <v>6980897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121392173</v>
+        <v>121393568</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502708</v>
+        <v>502665</v>
       </c>
       <c r="R4" t="n">
-        <v>6980897</v>
+        <v>6980853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393568</v>
+        <v>121392324</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502665</v>
+        <v>502722</v>
       </c>
       <c r="R5" t="n">
-        <v>6980853</v>
+        <v>6980906</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>121391948</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392512</v>
+        <v>121392194</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502643</v>
+        <v>502707</v>
       </c>
       <c r="R7" t="n">
-        <v>6980884</v>
+        <v>6980905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,6 +1332,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121393565</v>
+        <v>121392997</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502666</v>
+        <v>502612</v>
       </c>
       <c r="R8" t="n">
-        <v>6980854</v>
+        <v>6980880</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392194</v>
+        <v>121392512</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,37 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502707</v>
+        <v>502643</v>
       </c>
       <c r="R9" t="n">
-        <v>6980905</v>
+        <v>6980884</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121393539</v>
+        <v>121393565</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502656</v>
+        <v>502666</v>
       </c>
       <c r="R10" t="n">
-        <v>6980868</v>
+        <v>6980854</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392330</v>
+        <v>121393539</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502707</v>
+        <v>502656</v>
       </c>
       <c r="R11" t="n">
-        <v>6980894</v>
+        <v>6980868</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121392330</v>
       </c>
       <c r="B2" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392173</v>
+        <v>121393539</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502708</v>
+        <v>502656</v>
       </c>
       <c r="R3" t="n">
-        <v>6980897</v>
+        <v>6980868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393568</v>
+        <v>121392324</v>
       </c>
       <c r="B4" t="n">
-        <v>90995</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502665</v>
+        <v>502722</v>
       </c>
       <c r="R4" t="n">
-        <v>6980853</v>
+        <v>6980906</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121392324</v>
+        <v>121391948</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502722</v>
+        <v>502812</v>
       </c>
       <c r="R5" t="n">
-        <v>6980906</v>
+        <v>6980986</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391948</v>
+        <v>121392997</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502812</v>
+        <v>502612</v>
       </c>
       <c r="R6" t="n">
-        <v>6980986</v>
+        <v>6980880</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392194</v>
+        <v>121393568</v>
       </c>
       <c r="B7" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,22 +1269,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502707</v>
+        <v>502665</v>
       </c>
       <c r="R7" t="n">
-        <v>6980905</v>
+        <v>6980853</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121392997</v>
+        <v>121393565</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502612</v>
+        <v>502666</v>
       </c>
       <c r="R8" t="n">
-        <v>6980880</v>
+        <v>6980854</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392512</v>
+        <v>121392194</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502643</v>
+        <v>502707</v>
       </c>
       <c r="R9" t="n">
-        <v>6980884</v>
+        <v>6980905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121393565</v>
+        <v>121392173</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502666</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6980854</v>
+        <v>6980897</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121393539</v>
+        <v>121392512</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502656</v>
+        <v>502643</v>
       </c>
       <c r="R11" t="n">
-        <v>6980868</v>
+        <v>6980884</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392330</v>
+        <v>121392173</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502707</v>
+        <v>502708</v>
       </c>
       <c r="R2" t="n">
-        <v>6980894</v>
+        <v>6980897</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121393539</v>
+        <v>121391948</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502656</v>
+        <v>502812</v>
       </c>
       <c r="R3" t="n">
-        <v>6980868</v>
+        <v>6980986</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121392324</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391948</v>
+        <v>121392330</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>90999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502812</v>
+        <v>502707</v>
       </c>
       <c r="R5" t="n">
-        <v>6980986</v>
+        <v>6980894</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392997</v>
+        <v>121392512</v>
       </c>
       <c r="B6" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502612</v>
+        <v>502643</v>
       </c>
       <c r="R6" t="n">
-        <v>6980880</v>
+        <v>6980884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121393568</v>
+        <v>121392997</v>
       </c>
       <c r="B7" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502665</v>
+        <v>502612</v>
       </c>
       <c r="R7" t="n">
-        <v>6980853</v>
+        <v>6980880</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>121393565</v>
       </c>
       <c r="B8" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392194</v>
+        <v>121393568</v>
       </c>
       <c r="B9" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,22 +1493,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502707</v>
+        <v>502665</v>
       </c>
       <c r="R9" t="n">
-        <v>6980905</v>
+        <v>6980853</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1553,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392173</v>
+        <v>121392194</v>
       </c>
       <c r="B10" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,34 +1587,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502708</v>
+        <v>502707</v>
       </c>
       <c r="R10" t="n">
-        <v>6980897</v>
+        <v>6980905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,6 +1668,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392512</v>
+        <v>121393539</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502643</v>
+        <v>502656</v>
       </c>
       <c r="R11" t="n">
-        <v>6980884</v>
+        <v>6980868</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392173</v>
+        <v>121391948</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502708</v>
+        <v>502812</v>
       </c>
       <c r="R2" t="n">
-        <v>6980897</v>
+        <v>6980986</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121391948</v>
+        <v>121392324</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502812</v>
+        <v>502722</v>
       </c>
       <c r="R3" t="n">
-        <v>6980986</v>
+        <v>6980906</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121392324</v>
+        <v>121393539</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502722</v>
+        <v>502656</v>
       </c>
       <c r="R4" t="n">
-        <v>6980906</v>
+        <v>6980868</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121392330</v>
+        <v>121393568</v>
       </c>
       <c r="B5" t="n">
         <v>90999</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502707</v>
+        <v>502665</v>
       </c>
       <c r="R5" t="n">
-        <v>6980894</v>
+        <v>6980853</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121393568</v>
+        <v>121392194</v>
       </c>
       <c r="B9" t="n">
         <v>90999</v>
@@ -1493,19 +1493,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502665</v>
+        <v>502707</v>
       </c>
       <c r="R9" t="n">
-        <v>6980853</v>
+        <v>6980905</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392194</v>
+        <v>121392173</v>
       </c>
       <c r="B10" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,37 +1591,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502707</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6980905</v>
+        <v>6980897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1669,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121393539</v>
+        <v>121392330</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>90999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502656</v>
+        <v>502707</v>
       </c>
       <c r="R11" t="n">
-        <v>6980868</v>
+        <v>6980894</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392324</v>
+        <v>121393539</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502722</v>
+        <v>502656</v>
       </c>
       <c r="R3" t="n">
-        <v>6980906</v>
+        <v>6980868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393539</v>
+        <v>121392324</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502656</v>
+        <v>502722</v>
       </c>
       <c r="R4" t="n">
-        <v>6980868</v>
+        <v>6980906</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121391948</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121393539</v>
+        <v>121392512</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502656</v>
+        <v>502643</v>
       </c>
       <c r="R3" t="n">
-        <v>6980868</v>
+        <v>6980884</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121392324</v>
+        <v>121392997</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502722</v>
+        <v>502612</v>
       </c>
       <c r="R4" t="n">
-        <v>6980906</v>
+        <v>6980880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393568</v>
+        <v>121393565</v>
       </c>
       <c r="B5" t="n">
-        <v>90999</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502665</v>
+        <v>502666</v>
       </c>
       <c r="R5" t="n">
-        <v>6980853</v>
+        <v>6980854</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392512</v>
+        <v>121392330</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502643</v>
+        <v>502707</v>
       </c>
       <c r="R6" t="n">
-        <v>6980884</v>
+        <v>6980894</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392997</v>
+        <v>121392173</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502612</v>
+        <v>502708</v>
       </c>
       <c r="R7" t="n">
-        <v>6980880</v>
+        <v>6980897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121393565</v>
+        <v>121392324</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502666</v>
+        <v>502722</v>
       </c>
       <c r="R8" t="n">
-        <v>6980854</v>
+        <v>6980906</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392194</v>
+        <v>121393539</v>
       </c>
       <c r="B9" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,40 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502707</v>
+        <v>502656</v>
       </c>
       <c r="R9" t="n">
-        <v>6980905</v>
+        <v>6980868</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1553,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392173</v>
+        <v>121392194</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,34 +1587,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502708</v>
+        <v>502707</v>
       </c>
       <c r="R10" t="n">
-        <v>6980897</v>
+        <v>6980905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,6 +1668,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392330</v>
+        <v>121393568</v>
       </c>
       <c r="B11" t="n">
-        <v>90999</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502707</v>
+        <v>502665</v>
       </c>
       <c r="R11" t="n">
-        <v>6980894</v>
+        <v>6980853</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121391948</v>
+        <v>121392512</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502812</v>
+        <v>502643</v>
       </c>
       <c r="R2" t="n">
-        <v>6980986</v>
+        <v>6980884</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392512</v>
+        <v>121392324</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502643</v>
+        <v>502722</v>
       </c>
       <c r="R3" t="n">
-        <v>6980884</v>
+        <v>6980906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121392997</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393565</v>
+        <v>121393539</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502666</v>
+        <v>502656</v>
       </c>
       <c r="R5" t="n">
-        <v>6980854</v>
+        <v>6980868</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392330</v>
+        <v>121393565</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502707</v>
+        <v>502666</v>
       </c>
       <c r="R6" t="n">
-        <v>6980894</v>
+        <v>6980854</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392173</v>
+        <v>121391948</v>
       </c>
       <c r="B7" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502708</v>
+        <v>502812</v>
       </c>
       <c r="R7" t="n">
-        <v>6980897</v>
+        <v>6980986</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121392324</v>
+        <v>121393568</v>
       </c>
       <c r="B8" t="n">
-        <v>90719</v>
+        <v>91006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502722</v>
+        <v>502665</v>
       </c>
       <c r="R8" t="n">
-        <v>6980906</v>
+        <v>6980853</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121393539</v>
+        <v>121392173</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502656</v>
+        <v>502708</v>
       </c>
       <c r="R9" t="n">
-        <v>6980868</v>
+        <v>6980897</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392194</v>
+        <v>121392330</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,9 +1605,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
@@ -1617,10 +1614,10 @@
         <v>502707</v>
       </c>
       <c r="R10" t="n">
-        <v>6980905</v>
+        <v>6980894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1665,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1687,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121393568</v>
+        <v>121392194</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,19 +1717,22 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502665</v>
+        <v>502707</v>
       </c>
       <c r="R11" t="n">
-        <v>6980853</v>
+        <v>6980905</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,6 +1780,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392512</v>
+        <v>121393539</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502643</v>
+        <v>502656</v>
       </c>
       <c r="R2" t="n">
-        <v>6980884</v>
+        <v>6980868</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121392997</v>
+        <v>121392512</v>
       </c>
       <c r="B4" t="n">
         <v>90720</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502612</v>
+        <v>502643</v>
       </c>
       <c r="R4" t="n">
-        <v>6980880</v>
+        <v>6980884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393539</v>
+        <v>121392330</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>91006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502656</v>
+        <v>502707</v>
       </c>
       <c r="R5" t="n">
-        <v>6980868</v>
+        <v>6980894</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121393565</v>
+        <v>121392194</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502666</v>
+        <v>502707</v>
       </c>
       <c r="R6" t="n">
-        <v>6980854</v>
+        <v>6980905</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391948</v>
+        <v>121392997</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502812</v>
+        <v>502612</v>
       </c>
       <c r="R7" t="n">
-        <v>6980986</v>
+        <v>6980880</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392330</v>
+        <v>121391948</v>
       </c>
       <c r="B10" t="n">
-        <v>91006</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502707</v>
+        <v>502812</v>
       </c>
       <c r="R10" t="n">
-        <v>6980894</v>
+        <v>6980986</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392194</v>
+        <v>121393565</v>
       </c>
       <c r="B11" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,40 +1703,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502707</v>
+        <v>502666</v>
       </c>
       <c r="R11" t="n">
-        <v>6980905</v>
+        <v>6980854</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1781,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121393539</v>
+        <v>121392512</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502656</v>
+        <v>502643</v>
       </c>
       <c r="R2" t="n">
-        <v>6980868</v>
+        <v>6980884</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392324</v>
+        <v>121393539</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502722</v>
+        <v>502656</v>
       </c>
       <c r="R3" t="n">
-        <v>6980906</v>
+        <v>6980868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121392512</v>
+        <v>121393568</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502643</v>
+        <v>502665</v>
       </c>
       <c r="R4" t="n">
-        <v>6980884</v>
+        <v>6980853</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121392330</v>
+        <v>121391948</v>
       </c>
       <c r="B5" t="n">
-        <v>91006</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502707</v>
+        <v>502812</v>
       </c>
       <c r="R5" t="n">
-        <v>6980894</v>
+        <v>6980986</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392194</v>
+        <v>121392997</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502707</v>
+        <v>502612</v>
       </c>
       <c r="R6" t="n">
-        <v>6980905</v>
+        <v>6980880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121392997</v>
+        <v>121393565</v>
       </c>
       <c r="B7" t="n">
         <v>90720</v>
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502612</v>
+        <v>502666</v>
       </c>
       <c r="R7" t="n">
-        <v>6980880</v>
+        <v>6980854</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121393568</v>
+        <v>121392324</v>
       </c>
       <c r="B8" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502665</v>
+        <v>502722</v>
       </c>
       <c r="R8" t="n">
-        <v>6980853</v>
+        <v>6980906</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392173</v>
+        <v>121392194</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502708</v>
+        <v>502707</v>
       </c>
       <c r="R9" t="n">
-        <v>6980897</v>
+        <v>6980905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121391948</v>
+        <v>121392173</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502812</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6980986</v>
+        <v>6980897</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121393565</v>
+        <v>121392330</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502666</v>
+        <v>502707</v>
       </c>
       <c r="R11" t="n">
-        <v>6980854</v>
+        <v>6980894</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392512</v>
+        <v>121392194</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502643</v>
+        <v>502707</v>
       </c>
       <c r="R2" t="n">
-        <v>6980884</v>
+        <v>6980905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121393539</v>
+        <v>121392997</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502656</v>
+        <v>502612</v>
       </c>
       <c r="R3" t="n">
-        <v>6980868</v>
+        <v>6980880</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393568</v>
+        <v>121393565</v>
       </c>
       <c r="B4" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502665</v>
+        <v>502666</v>
       </c>
       <c r="R4" t="n">
-        <v>6980853</v>
+        <v>6980854</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391948</v>
+        <v>121393539</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502812</v>
+        <v>502656</v>
       </c>
       <c r="R5" t="n">
-        <v>6980986</v>
+        <v>6980868</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392997</v>
+        <v>121392330</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502612</v>
+        <v>502707</v>
       </c>
       <c r="R6" t="n">
-        <v>6980880</v>
+        <v>6980894</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121393565</v>
+        <v>121393568</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502666</v>
+        <v>502665</v>
       </c>
       <c r="R7" t="n">
-        <v>6980854</v>
+        <v>6980853</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121392194</v>
+        <v>121391948</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,40 +1479,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502707</v>
+        <v>502812</v>
       </c>
       <c r="R9" t="n">
-        <v>6980905</v>
+        <v>6980986</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392173</v>
+        <v>121392512</v>
       </c>
       <c r="B10" t="n">
         <v>90720</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502708</v>
+        <v>502643</v>
       </c>
       <c r="R10" t="n">
-        <v>6980897</v>
+        <v>6980884</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392330</v>
+        <v>121392173</v>
       </c>
       <c r="B11" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502707</v>
+        <v>502708</v>
       </c>
       <c r="R11" t="n">
-        <v>6980894</v>
+        <v>6980897</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 54133-2024 artfynd.xlsx
+++ b/artfynd/A 54133-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121392194</v>
+        <v>121393539</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502707</v>
+        <v>502656</v>
       </c>
       <c r="R2" t="n">
-        <v>6980905</v>
+        <v>6980868</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121392997</v>
+        <v>121393568</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>91014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502612</v>
+        <v>502665</v>
       </c>
       <c r="R3" t="n">
-        <v>6980880</v>
+        <v>6980853</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121393565</v>
+        <v>121391948</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502666</v>
+        <v>502812</v>
       </c>
       <c r="R4" t="n">
-        <v>6980854</v>
+        <v>6980986</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121393539</v>
+        <v>121392194</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>91014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,37 +1027,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bällsta, Bällsta, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502656</v>
+        <v>502707</v>
       </c>
       <c r="R5" t="n">
-        <v>6980868</v>
+        <v>6980905</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121392330</v>
+        <v>121392997</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502707</v>
+        <v>502612</v>
       </c>
       <c r="R6" t="n">
-        <v>6980894</v>
+        <v>6980880</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121393568</v>
+        <v>121392512</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502665</v>
+        <v>502643</v>
       </c>
       <c r="R7" t="n">
-        <v>6980853</v>
+        <v>6980884</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
         <v>121392324</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121391948</v>
+        <v>121392330</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>91014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502812</v>
+        <v>502707</v>
       </c>
       <c r="R9" t="n">
-        <v>6980986</v>
+        <v>6980894</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121392512</v>
+        <v>121392173</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502643</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6980884</v>
+        <v>6980897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121392173</v>
+        <v>121393565</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502708</v>
+        <v>502666</v>
       </c>
       <c r="R11" t="n">
-        <v>6980897</v>
+        <v>6980854</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
